--- a/outputs/33722.xlsx
+++ b/outputs/33722.xlsx
@@ -71,12 +71,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.00%"/>
-    <numFmt numFmtId="167" formatCode="0"/>
-    <numFmt numFmtId="168" formatCode="\$#,##0_);[RED]&quot;($&quot;#,##0\)"/>
+    <numFmt numFmtId="166" formatCode="0%"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
+    <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="\$#,##0_);[RED]&quot;($&quot;#,##0\)"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -153,44 +154,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -463,7 +466,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.43"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -473,12 +476,12 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="n">
@@ -487,13 +490,13 @@
       <c r="C2" s="4" t="n">
         <v>0.000999500249875062</v>
       </c>
-      <c r="E2" s="7" t="n">
-        <f aca="false" t="array" ref="E2:E2">MEDIAN(IF(C2:C12&lt;0.01,B2:B12))</f>
+      <c r="E2" s="6" t="n">
+        <f aca="false" t="array" ref="E2:E2">MEDIAN(IF((C2:C12&gt;=0)*(C2:C12&lt;=0.01),B2:B12))</f>
         <v>119300000</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="3" t="n">
@@ -502,13 +505,13 @@
       <c r="C3" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="E3" s="7" t="n">
-        <f aca="false" t="array" ref="E3:E3">MEDIAN(IF(C3:C12&lt;0.01,B3:B12))</f>
+      <c r="E3" s="6" t="n">
+        <f aca="false" t="array" ref="E3:E3">MEDIAN(IF((C3:C12&gt;=0)*(C3:C12&lt;=0.01),B3:B12))</f>
         <v>310750000</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3" t="n">
@@ -517,13 +520,13 @@
       <c r="C4" s="4" t="n">
         <v>0.120939530234883</v>
       </c>
-      <c r="E4" s="7" t="n">
-        <f aca="false" t="array" ref="E4:E4">MEDIAN(IF(C4:C12&lt;0.01,B4:B12))</f>
+      <c r="E4" s="6" t="n">
+        <f aca="false" t="array" ref="E4:E4">MEDIAN(IF((C4:C12&gt;=0)*(C4:C12&lt;=0.01),B4:B12))</f>
         <v>502200000</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="3" t="n">
@@ -532,13 +535,13 @@
       <c r="C5" s="4" t="n">
         <v>0.589705147426287</v>
       </c>
-      <c r="E5" s="7" t="n">
-        <f aca="false" t="array" ref="E5:E5">MEDIAN(IF(C5:C12&lt;0.01,B5:B12))</f>
+      <c r="E5" s="6" t="n">
+        <f aca="false" t="array" ref="E5:E5">MEDIAN(IF((C5:C12&gt;=0)*(C5:C12&lt;=0.01),B5:B12))</f>
         <v>502200000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="3" t="n">
@@ -547,13 +550,13 @@
       <c r="C6" s="4" t="n">
         <v>0.00149925037481259</v>
       </c>
-      <c r="E6" s="7" t="n">
-        <f aca="false" t="array" ref="E6:E6">MEDIAN(IF(C6:C12&lt;0.01,B6:B12))</f>
+      <c r="E6" s="6" t="n">
+        <f aca="false" t="array" ref="E6:E6">MEDIAN(IF((C6:C12&gt;=0)*(C6:C12&lt;=0.01),B6:B12))</f>
         <v>502200000</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="3" t="n">
@@ -563,8 +566,8 @@
         <v>0.159420289855073</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="3" t="n">
@@ -574,8 +577,8 @@
         <v>0.0809595202398801</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="3" t="n">
@@ -585,8 +588,8 @@
         <v>0.654172913543228</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="3" t="n">
@@ -596,22 +599,22 @@
         <v>0.334332833583208</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="7" t="n">
         <v>5000000</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.482758620689655</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="7" t="n">
         <v>5000000</v>
       </c>
       <c r="C12" s="4" t="n">
